--- a/resources/dropshipping/files/drop-basics-costing-sheet.xlsx
+++ b/resources/dropshipping/files/drop-basics-costing-sheet.xlsx
@@ -727,7 +727,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
